--- a/output/pdf_financials_xlsx/WHN.xlsx
+++ b/output/pdf_financials_xlsx/WHN.xlsx
@@ -5754,49 +5754,49 @@
         <v>0.128</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.164856</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.174099</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.231844</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.218473</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.179599</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.306614</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.851083</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.775682</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.042747</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.692895</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.617543</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.862832</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.247822</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.343773</v>
       </c>
     </row>
     <row r="93">
@@ -9920,7 +9920,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -12324,7 +12328,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13566,7 +13574,11 @@
           <t>Reserves (note 7) 128,000</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WHN.xlsx
+++ b/output/pdf_financials_xlsx/WHN.xlsx
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005004</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001689</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002139</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1044,31 +1044,31 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.0006400000000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000593</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.02087</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.060524</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.024322</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.08165799999999999</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.183933</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.01213</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.008427</v>
       </c>
     </row>
     <row r="13">
@@ -1961,7 +1961,7 @@
         <v>-0.186134</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.186134</v>
+        <v>-0.191138</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.300972</v>
+        <v>-0.303111</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.002297</v>
@@ -1983,31 +1983,31 @@
         <v>-0.406408</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.407831</v>
+        <v>-0.408471</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.02282</v>
+        <v>-3.023413</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.669363</v>
+        <v>-1.690233</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.669363</v>
+        <v>-1.729887</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.049316</v>
+        <v>-2.073638</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.249352</v>
+        <v>-1.33101</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.405141</v>
+        <v>-3.589074</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.945214</v>
+        <v>-3.957344</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.651688</v>
+        <v>-3.660115</v>
       </c>
     </row>
     <row r="28">
@@ -2077,7 +2077,7 @@
         <v>-0.186134</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.186134</v>
+        <v>-0.191138</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.300972</v>
+        <v>-0.303111</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.002297</v>
@@ -2099,31 +2099,31 @@
         <v>-0.406408</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.407831</v>
+        <v>-0.408471</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.02282</v>
+        <v>-3.023413</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.669363</v>
+        <v>-1.690233</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.669363</v>
+        <v>-1.729887</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.049316</v>
+        <v>-2.073638</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.249352</v>
+        <v>-1.33101</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.405141</v>
+        <v>-3.589074</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.945214</v>
+        <v>-3.957344</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.651688</v>
+        <v>-3.660115</v>
       </c>
     </row>
     <row r="30">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.916602</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.394146</v>
@@ -2388,10 +2388,10 @@
         <v>0.016174</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.391093</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.059514</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.916602</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.394146</v>
@@ -2498,10 +2498,10 @@
         <v>0.016174</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.391093</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.059514</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.916946</v>
+        <v>0.000344</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -3158,10 +3158,10 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.0071</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.391093</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -8876,7 +8876,11 @@
           <t>Reclamation Deposits (note 7)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -11810,7 +11814,11 @@
           <t>Reclamation Deposits</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12508,7 +12516,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
@@ -16356,7 +16364,11 @@
           <t>Expenditures on reclamation deposits</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -20370,7 +20382,11 @@
           <t>Expenditures (refund) of reclamation deposit</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -21404,7 +21420,11 @@
           <t>Refund (expenditures) of reclamation deposit</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -25274,7 +25294,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -42780,7 +42800,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -47590,7 +47610,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
